--- a/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00365</v>
+        <v>0.0733</v>
       </c>
       <c r="E2">
-        <v>-0.0597</v>
+        <v>0.0617</v>
       </c>
       <c r="F2">
-        <v>0.779</v>
+        <v>0.216</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2110.9</v>
+        <v>3562.2</v>
       </c>
       <c r="L2">
-        <v>0.283631624207245</v>
+        <v>0.3440542420027816</v>
       </c>
       <c r="M2">
-        <v>262.984</v>
+        <v>1536.212</v>
       </c>
       <c r="N2">
-        <v>0.009220552916221095</v>
+        <v>0.05349393227126317</v>
       </c>
       <c r="O2">
-        <v>0.124583826803733</v>
+        <v>0.4312537196114761</v>
       </c>
       <c r="P2">
-        <v>247.895</v>
+        <v>1515.3</v>
       </c>
       <c r="Q2">
-        <v>0.008691513419700926</v>
+        <v>0.05276573517889788</v>
       </c>
       <c r="R2">
-        <v>0.1174356909375148</v>
+        <v>0.4253831901633822</v>
       </c>
       <c r="S2">
-        <v>15.089</v>
+        <v>20.91199999999998</v>
       </c>
       <c r="T2">
-        <v>0.05737611413622121</v>
+        <v>0.01361270449651479</v>
       </c>
       <c r="U2">
-        <v>26066.6</v>
+        <v>18800.4</v>
       </c>
       <c r="V2">
-        <v>0.9139280893361149</v>
+        <v>0.6546670148863933</v>
       </c>
       <c r="W2">
-        <v>0.09614712393676934</v>
+        <v>0.1903365337352951</v>
       </c>
       <c r="X2">
-        <v>0.07772752934082455</v>
+        <v>0.1152811821711793</v>
       </c>
       <c r="Y2">
-        <v>0.01841959459594479</v>
+        <v>0.07505535156411583</v>
       </c>
       <c r="Z2">
-        <v>0.2640300556625763</v>
+        <v>0.342845789595682</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05166547295568482</v>
+        <v>0.08022494305440167</v>
       </c>
       <c r="AC2">
-        <v>-0.05166547295568482</v>
+        <v>-0.08022494305440167</v>
       </c>
       <c r="AD2">
-        <v>38649.3</v>
+        <v>30634.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>38649.3</v>
+        <v>30634.6</v>
       </c>
       <c r="AG2">
-        <v>12582.7</v>
+        <v>11834.2</v>
       </c>
       <c r="AH2">
-        <v>0.5753884128222383</v>
+        <v>0.5161502288882786</v>
       </c>
       <c r="AI2">
-        <v>0.6809357442242742</v>
+        <v>0.6033330969993461</v>
       </c>
       <c r="AJ2">
-        <v>0.3061171364483435</v>
+        <v>0.2918299356130569</v>
       </c>
       <c r="AK2">
-        <v>0.4099600879693737</v>
+        <v>0.370105581825915</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scotiabank Perú S.A.A. (BVL:SCOTIAC1)</t>
+          <t>Credicorp Ltd. (NYSE:BAP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0446</v>
+        <v>0.0551</v>
       </c>
       <c r="E3">
-        <v>-0.116</v>
+        <v>0.0333</v>
+      </c>
+      <c r="F3">
+        <v>0.216</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,82 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>145.3</v>
+        <v>1161.7</v>
       </c>
       <c r="L3">
-        <v>0.2371857655892916</v>
+        <v>0.3060004214519018</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>421.9</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03910283145650864</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3631746578290436</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>401</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03716576301033412</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3451837823878798</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>20.89999999999998</v>
+      </c>
+      <c r="T3">
+        <v>0.04953780516710116</v>
       </c>
       <c r="U3">
-        <v>652.4</v>
+        <v>4579.6</v>
       </c>
       <c r="V3">
-        <v>0.147298548237791</v>
+        <v>0.424449696464155</v>
       </c>
       <c r="W3">
-        <v>0.05106846618866864</v>
+        <v>0.1903365337352951</v>
       </c>
       <c r="X3">
-        <v>0.07369127278128104</v>
+        <v>0.0943981625433585</v>
       </c>
       <c r="Y3">
-        <v>-0.0226228065926124</v>
+        <v>0.0959383711919366</v>
       </c>
       <c r="Z3">
-        <v>0.1634297300181411</v>
+        <v>0.2976284739916115</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05083353259281786</v>
+        <v>0.07922348965349107</v>
       </c>
       <c r="AC3">
-        <v>-0.05083353259281786</v>
+        <v>-0.07922348965349107</v>
       </c>
       <c r="AD3">
-        <v>4881.5</v>
+        <v>6827.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4881.5</v>
+        <v>6827.3</v>
       </c>
       <c r="AG3">
-        <v>4229.1</v>
+        <v>2247.7</v>
       </c>
       <c r="AH3">
-        <v>0.5242948896956158</v>
+        <v>0.3875448435584216</v>
       </c>
       <c r="AI3">
-        <v>0.6585586314823809</v>
+        <v>0.49529177911262</v>
       </c>
       <c r="AJ3">
-        <v>0.488450255249359</v>
+        <v>0.1724066517350351</v>
       </c>
       <c r="AK3">
-        <v>0.6256065088757397</v>
+        <v>0.2441878150530158</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00445</v>
+        <v>0.0733</v>
       </c>
       <c r="E4">
-        <v>-0.06469999999999999</v>
+        <v>0.0794</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,82 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>495.1</v>
+        <v>1120.8</v>
       </c>
       <c r="L4">
-        <v>0.2524346096976495</v>
+        <v>0.3652360934597713</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>342.8</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04124505191726927</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.3058529621698787</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>342.8</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04124505191726927</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.3058529621698787</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>9958.200000000001</v>
+        <v>8405.9</v>
       </c>
       <c r="V4">
-        <v>1.211135705772178</v>
+        <v>1.011382094257216</v>
       </c>
       <c r="W4">
-        <v>0.09614712393676934</v>
+        <v>0.2391652262979322</v>
       </c>
       <c r="X4">
-        <v>0.07760700914154922</v>
+        <v>0.1092309904204952</v>
       </c>
       <c r="Y4">
-        <v>0.01854011479522012</v>
+        <v>0.129934235877437</v>
       </c>
       <c r="Z4">
-        <v>0.2251262626262627</v>
+        <v>0.592962590817746</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05101943373475137</v>
+        <v>0.08000763580377318</v>
       </c>
       <c r="AC4">
-        <v>-0.05101943373475137</v>
+        <v>-0.08000763580377318</v>
       </c>
       <c r="AD4">
-        <v>10447.1</v>
+        <v>9807.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10447.1</v>
+        <v>9807.4</v>
       </c>
       <c r="AG4">
-        <v>488.8999999999996</v>
+        <v>1401.5</v>
       </c>
       <c r="AH4">
-        <v>0.5595871296727782</v>
+        <v>0.5412860746080017</v>
       </c>
       <c r="AI4">
-        <v>0.6903339632865053</v>
+        <v>0.6424383757262919</v>
       </c>
       <c r="AJ4">
-        <v>0.05612379607627046</v>
+        <v>0.1442941273371222</v>
       </c>
       <c r="AK4">
-        <v>0.09446977894574116</v>
+        <v>0.2043002915451895</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -942,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banco BBVA Perú, S.A. (BVL:BBVAC1)</t>
+          <t>Scotiabank Perú S.A.A. (BVL:SCOTIAC1)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -951,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00365</v>
+        <v>0.029</v>
       </c>
       <c r="E5">
-        <v>-0.0597</v>
+        <v>0.0323</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>239.2</v>
+        <v>354.5</v>
       </c>
       <c r="L5">
-        <v>0.2748477536481673</v>
+        <v>0.3687330975660495</v>
       </c>
       <c r="M5">
-        <v>71.2</v>
+        <v>309.8</v>
       </c>
       <c r="N5">
-        <v>0.0232330483586765</v>
+        <v>0.08646627033966899</v>
       </c>
       <c r="O5">
-        <v>0.2976588628762542</v>
+        <v>0.8739069111424542</v>
       </c>
       <c r="P5">
-        <v>71.2</v>
+        <v>309.8</v>
       </c>
       <c r="Q5">
-        <v>0.0232330483586765</v>
+        <v>0.08646627033966899</v>
       </c>
       <c r="R5">
-        <v>0.2976588628762542</v>
+        <v>0.8739069111424542</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -999,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5162.7</v>
+        <v>574.4</v>
       </c>
       <c r="V5">
-        <v>1.684624420805325</v>
+        <v>0.1603170615981467</v>
       </c>
       <c r="W5">
-        <v>0.09321175278622088</v>
+        <v>0.141066454436928</v>
       </c>
       <c r="X5">
-        <v>0.09797839143104928</v>
+        <v>0.1152811821711793</v>
       </c>
       <c r="Y5">
-        <v>-0.004766638644828403</v>
+        <v>0.0257852722657487</v>
       </c>
       <c r="Z5">
-        <v>0.231752456528107</v>
+        <v>0.1456093054251355</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05166547295568482</v>
+        <v>0.08022494305440167</v>
       </c>
       <c r="AC5">
-        <v>-0.05166547295568482</v>
+        <v>-0.08022494305440167</v>
       </c>
       <c r="AD5">
-        <v>6579.6</v>
+        <v>5027.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6579.6</v>
+        <v>5027.6</v>
       </c>
       <c r="AG5">
-        <v>1416.900000000001</v>
+        <v>4453.200000000001</v>
       </c>
       <c r="AH5">
-        <v>0.6822338815039091</v>
+        <v>0.5838917600603915</v>
       </c>
       <c r="AI5">
-        <v>0.7417143887811698</v>
+        <v>0.6573744769874478</v>
       </c>
       <c r="AJ5">
-        <v>0.3161664621220575</v>
+        <v>0.5541494008287603</v>
       </c>
       <c r="AK5">
-        <v>0.3821094360993502</v>
+        <v>0.6295521375254468</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1064,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Credicorp Ltd. (NYSE:BAP)</t>
+          <t>Banco BBVA Perú, S.A. (BVL:BBVAC1)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1073,13 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0238</v>
+        <v>0.0843</v>
       </c>
       <c r="E6">
-        <v>-0.0106</v>
-      </c>
-      <c r="F6">
-        <v>0.779</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,85 +1100,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>769.8</v>
+        <v>542.7</v>
       </c>
       <c r="L6">
-        <v>0.2639917695473251</v>
+        <v>0.4060606060606061</v>
       </c>
       <c r="M6">
-        <v>110.495</v>
+        <v>272.8</v>
       </c>
       <c r="N6">
-        <v>0.0113834916448602</v>
+        <v>0.08329008029798797</v>
       </c>
       <c r="O6">
-        <v>0.1435372824110158</v>
+        <v>0.5026718260549106</v>
       </c>
       <c r="P6">
-        <v>96.19499999999999</v>
+        <v>272.8</v>
       </c>
       <c r="Q6">
-        <v>0.009910267240846433</v>
+        <v>0.08329008029798797</v>
       </c>
       <c r="R6">
-        <v>0.1249610288386594</v>
+        <v>0.5026718260549106</v>
       </c>
       <c r="S6">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.1294176207068193</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>5531.2</v>
+        <v>4283.6</v>
       </c>
       <c r="V6">
-        <v>0.5698390785651</v>
+        <v>1.307849662626324</v>
       </c>
       <c r="W6">
-        <v>0.1173260988843504</v>
+        <v>0.236862779329609</v>
       </c>
       <c r="X6">
-        <v>0.07772752934082455</v>
+        <v>0.1158359007584044</v>
       </c>
       <c r="Y6">
-        <v>0.03959856954352586</v>
+        <v>0.1210268785712045</v>
       </c>
       <c r="Z6">
-        <v>0.3202389711938676</v>
+        <v>0.3604271729457135</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05177984211311185</v>
+        <v>0.08024286393926255</v>
       </c>
       <c r="AC6">
-        <v>-0.05177984211311185</v>
+        <v>-0.08024286393926255</v>
       </c>
       <c r="AD6">
-        <v>12383.5</v>
+        <v>4663</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12383.5</v>
+        <v>4663</v>
       </c>
       <c r="AG6">
-        <v>6852.3</v>
+        <v>379.3999999999996</v>
       </c>
       <c r="AH6">
-        <v>0.5605904907628304</v>
+        <v>0.5874053638688383</v>
       </c>
       <c r="AI6">
-        <v>0.6653789116231087</v>
+        <v>0.6321340454952146</v>
       </c>
       <c r="AJ6">
-        <v>0.413813719510354</v>
+        <v>0.1038115303581688</v>
       </c>
       <c r="AK6">
-        <v>0.5238761467889909</v>
+        <v>0.1226640801810539</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1198,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.104</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="E7">
-        <v>0.236</v>
+        <v>0.0617</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,85 +1222,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>461.5</v>
+        <v>382.5</v>
       </c>
       <c r="L7">
-        <v>0.4264461282572537</v>
+        <v>0.3212665882748195</v>
       </c>
       <c r="M7">
-        <v>81.289</v>
+        <v>188.912</v>
       </c>
       <c r="N7">
-        <v>0.02623071958696354</v>
+        <v>0.06848359615733189</v>
       </c>
       <c r="O7">
-        <v>0.1761408450704225</v>
+        <v>0.4938875816993464</v>
       </c>
       <c r="P7">
-        <v>80.5</v>
+        <v>188.9</v>
       </c>
       <c r="Q7">
-        <v>0.02597612132946112</v>
+        <v>0.06847924596701106</v>
       </c>
       <c r="R7">
-        <v>0.1744312026002167</v>
+        <v>0.4938562091503268</v>
       </c>
       <c r="S7">
-        <v>0.7890000000000015</v>
+        <v>0.01200000000000045</v>
       </c>
       <c r="T7">
-        <v>0.009706110297826292</v>
+        <v>6.352163970526199e-05</v>
       </c>
       <c r="U7">
-        <v>4762.1</v>
+        <v>956.9</v>
       </c>
       <c r="V7">
-        <v>1.536656986124556</v>
+        <v>0.3468914264999093</v>
       </c>
       <c r="W7">
-        <v>0.2001561347963742</v>
+        <v>0.1619321789932687</v>
       </c>
       <c r="X7">
-        <v>0.08075752275831051</v>
+        <v>0.1195900339795681</v>
       </c>
       <c r="Y7">
-        <v>0.1193986120380637</v>
+        <v>0.04234214501370064</v>
       </c>
       <c r="Z7">
-        <v>0.377559920454942</v>
+        <v>0.6081937065794849</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05259210359162662</v>
+        <v>0.08125929503154064</v>
       </c>
       <c r="AC7">
-        <v>-0.05259210359162662</v>
+        <v>-0.08125929503154064</v>
       </c>
       <c r="AD7">
-        <v>4357.6</v>
+        <v>4309.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4357.6</v>
+        <v>4309.3</v>
       </c>
       <c r="AG7">
-        <v>-404.5</v>
+        <v>3352.4</v>
       </c>
       <c r="AH7">
-        <v>0.5843950325885793</v>
+        <v>0.6097088202835395</v>
       </c>
       <c r="AI7">
-        <v>0.6473638078825784</v>
+        <v>0.6431119136806602</v>
       </c>
       <c r="AJ7">
-        <v>-0.1501206160697718</v>
+        <v>0.5485934968662555</v>
       </c>
       <c r="AK7">
-        <v>-0.2054133658338412</v>
+        <v>0.5836554197569553</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0733</v>
+        <v>0.0626</v>
       </c>
       <c r="E2">
-        <v>0.0617</v>
+        <v>0.0418</v>
       </c>
       <c r="F2">
-        <v>0.216</v>
+        <v>0.112</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3562.2</v>
+        <v>3690.8</v>
       </c>
       <c r="L2">
-        <v>0.3440542420027816</v>
+        <v>0.328541290201978</v>
       </c>
       <c r="M2">
-        <v>1536.212</v>
+        <v>1995</v>
       </c>
       <c r="N2">
-        <v>0.05349393227126317</v>
+        <v>0.06564270625629282</v>
       </c>
       <c r="O2">
-        <v>0.4312537196114761</v>
+        <v>0.5405332177305733</v>
       </c>
       <c r="P2">
-        <v>1515.3</v>
+        <v>1951</v>
       </c>
       <c r="Q2">
-        <v>0.05276573517889788</v>
+        <v>0.06419494732131693</v>
       </c>
       <c r="R2">
-        <v>0.4253831901633822</v>
+        <v>0.528611683103934</v>
       </c>
       <c r="S2">
-        <v>20.91199999999998</v>
+        <v>44.00000000000003</v>
       </c>
       <c r="T2">
-        <v>0.01361270449651479</v>
+        <v>0.02205513784461154</v>
       </c>
       <c r="U2">
-        <v>18800.4</v>
+        <v>14046.4</v>
       </c>
       <c r="V2">
-        <v>0.6546670148863933</v>
+        <v>0.4621772978237551</v>
       </c>
       <c r="W2">
-        <v>0.1903365337352951</v>
+        <v>0.1863576061320755</v>
       </c>
       <c r="X2">
-        <v>0.1152811821711793</v>
+        <v>0.08729077069043828</v>
       </c>
       <c r="Y2">
-        <v>0.07505535156411583</v>
+        <v>0.09906683544163719</v>
       </c>
       <c r="Z2">
-        <v>0.342845789595682</v>
+        <v>0.3589243038071747</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08022494305440167</v>
+        <v>0.06776231979339066</v>
       </c>
       <c r="AC2">
-        <v>-0.08022494305440167</v>
+        <v>-0.06776231979339066</v>
       </c>
       <c r="AD2">
-        <v>30634.6</v>
+        <v>30689.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30634.6</v>
+        <v>30689.2</v>
       </c>
       <c r="AG2">
-        <v>11834.2</v>
+        <v>16642.8</v>
       </c>
       <c r="AH2">
-        <v>0.5161502288882786</v>
+        <v>0.502434472258149</v>
       </c>
       <c r="AI2">
-        <v>0.6033330969993461</v>
+        <v>0.5670395293578557</v>
       </c>
       <c r="AJ2">
-        <v>0.2918299356130569</v>
+        <v>0.3538416399841818</v>
       </c>
       <c r="AK2">
-        <v>0.370105581825915</v>
+        <v>0.4152871836588031</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0551</v>
+        <v>0.0626</v>
       </c>
       <c r="E3">
-        <v>0.0333</v>
+        <v>0.0418</v>
       </c>
       <c r="F3">
-        <v>0.216</v>
+        <v>0.112</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1161.7</v>
+        <v>1326.3</v>
       </c>
       <c r="L3">
-        <v>0.3060004214519018</v>
+        <v>0.3060857123075857</v>
       </c>
       <c r="M3">
-        <v>421.9</v>
+        <v>549.5</v>
       </c>
       <c r="N3">
-        <v>0.03910283145650864</v>
+        <v>0.04608082383623906</v>
       </c>
       <c r="O3">
-        <v>0.3631746578290436</v>
+        <v>0.4143104878232677</v>
       </c>
       <c r="P3">
-        <v>401</v>
+        <v>526.9</v>
       </c>
       <c r="Q3">
-        <v>0.03716576301033412</v>
+        <v>0.04418559796053569</v>
       </c>
       <c r="R3">
-        <v>0.3451837823878798</v>
+        <v>0.3972706024278067</v>
       </c>
       <c r="S3">
-        <v>20.89999999999998</v>
+        <v>22.60000000000002</v>
       </c>
       <c r="T3">
-        <v>0.04953780516710116</v>
+        <v>0.04112829845313926</v>
       </c>
       <c r="U3">
-        <v>4579.6</v>
+        <v>3501.9</v>
       </c>
       <c r="V3">
-        <v>0.424449696464155</v>
+        <v>0.2936677652267982</v>
       </c>
       <c r="W3">
-        <v>0.1903365337352951</v>
+        <v>0.1946405247941768</v>
       </c>
       <c r="X3">
-        <v>0.0943981625433585</v>
+        <v>0.08267412208850056</v>
       </c>
       <c r="Y3">
-        <v>0.0959383711919366</v>
+        <v>0.1119664027056762</v>
       </c>
       <c r="Z3">
-        <v>0.2976284739916115</v>
+        <v>0.4888590543452508</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07922348965349107</v>
+        <v>0.06756868562128299</v>
       </c>
       <c r="AC3">
-        <v>-0.07922348965349107</v>
+        <v>-0.06756868562128299</v>
       </c>
       <c r="AD3">
-        <v>6827.3</v>
+        <v>10259.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6827.3</v>
+        <v>10259.4</v>
       </c>
       <c r="AG3">
-        <v>2247.7</v>
+        <v>6757.5</v>
       </c>
       <c r="AH3">
-        <v>0.3875448435584216</v>
+        <v>0.4624663610423682</v>
       </c>
       <c r="AI3">
-        <v>0.49529177911262</v>
+        <v>0.5488922535324299</v>
       </c>
       <c r="AJ3">
-        <v>0.1724066517350351</v>
+        <v>0.3617079358962006</v>
       </c>
       <c r="AK3">
-        <v>0.2441878150530158</v>
+        <v>0.4448884733889869</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0733</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="E4">
-        <v>0.0794</v>
+        <v>0.0805</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1120.8</v>
+        <v>1269.7</v>
       </c>
       <c r="L4">
-        <v>0.3652360934597713</v>
+        <v>0.3646048702044567</v>
       </c>
       <c r="M4">
-        <v>342.8</v>
+        <v>711</v>
       </c>
       <c r="N4">
-        <v>0.04124505191726927</v>
+        <v>0.07268526564368885</v>
       </c>
       <c r="O4">
-        <v>0.3058529621698787</v>
+        <v>0.559974797196188</v>
       </c>
       <c r="P4">
-        <v>342.8</v>
+        <v>711</v>
       </c>
       <c r="Q4">
-        <v>0.04124505191726927</v>
+        <v>0.07268526564368885</v>
       </c>
       <c r="R4">
-        <v>0.3058529621698787</v>
+        <v>0.559974797196188</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8405.9</v>
+        <v>7874.4</v>
       </c>
       <c r="V4">
-        <v>1.011382094257216</v>
+        <v>0.8049969842259683</v>
       </c>
       <c r="W4">
-        <v>0.2391652262979322</v>
+        <v>0.2340676560051618</v>
       </c>
       <c r="X4">
-        <v>0.1092309904204952</v>
+        <v>0.08299781168955206</v>
       </c>
       <c r="Y4">
-        <v>0.129934235877437</v>
+        <v>0.1510698443156097</v>
       </c>
       <c r="Z4">
-        <v>0.592962590817746</v>
+        <v>0.520530335869419</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08000763580377318</v>
+        <v>0.06758387462960216</v>
       </c>
       <c r="AC4">
-        <v>-0.08000763580377318</v>
+        <v>-0.06758387462960216</v>
       </c>
       <c r="AD4">
-        <v>9807.4</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9807.4</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="AG4">
-        <v>1401.5</v>
+        <v>705.8999999999996</v>
       </c>
       <c r="AH4">
-        <v>0.5412860746080017</v>
+        <v>0.4672806090773437</v>
       </c>
       <c r="AI4">
-        <v>0.6424383757262919</v>
+        <v>0.5805816439765069</v>
       </c>
       <c r="AJ4">
-        <v>0.1442941273371222</v>
+        <v>0.06730677549152346</v>
       </c>
       <c r="AK4">
-        <v>0.2043002915451895</v>
+        <v>0.1022391518452001</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scotiabank Perú S.A.A. (BVL:SCOTIAC1)</t>
+          <t>Banco BBVA Perú, S.A. (BVL:BBVAC1)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.029</v>
+        <v>0.0716</v>
       </c>
       <c r="E5">
-        <v>0.0323</v>
+        <v>0.062</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>354.5</v>
+        <v>505.7</v>
       </c>
       <c r="L5">
-        <v>0.3687330975660495</v>
+        <v>0.3542805100182149</v>
       </c>
       <c r="M5">
-        <v>309.8</v>
+        <v>252.3</v>
       </c>
       <c r="N5">
-        <v>0.08646627033966899</v>
+        <v>0.07187419878642851</v>
       </c>
       <c r="O5">
-        <v>0.8739069111424542</v>
+        <v>0.4989123986553293</v>
       </c>
       <c r="P5">
-        <v>309.8</v>
+        <v>252.3</v>
       </c>
       <c r="Q5">
-        <v>0.08646627033966899</v>
+        <v>0.07187419878642851</v>
       </c>
       <c r="R5">
-        <v>0.8739069111424542</v>
+        <v>0.4989123986553293</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>574.4</v>
+        <v>1082.4</v>
       </c>
       <c r="V5">
-        <v>0.1603170615981467</v>
+        <v>0.3083497136996838</v>
       </c>
       <c r="W5">
-        <v>0.141066454436928</v>
+        <v>0.1863576061320755</v>
       </c>
       <c r="X5">
-        <v>0.1152811821711793</v>
+        <v>0.08729077069043828</v>
       </c>
       <c r="Y5">
-        <v>0.0257852722657487</v>
+        <v>0.09906683544163719</v>
       </c>
       <c r="Z5">
-        <v>0.1456093054251355</v>
+        <v>0.4614936954413191</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08022494305440167</v>
+        <v>0.06776231979339066</v>
       </c>
       <c r="AC5">
-        <v>-0.08022494305440167</v>
+        <v>-0.06776231979339066</v>
       </c>
       <c r="AD5">
-        <v>5027.6</v>
+        <v>3861.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5027.6</v>
+        <v>3861.8</v>
       </c>
       <c r="AG5">
-        <v>4453.200000000001</v>
+        <v>2779.4</v>
       </c>
       <c r="AH5">
-        <v>0.5838917600603915</v>
+        <v>0.5238398828013727</v>
       </c>
       <c r="AI5">
-        <v>0.6573744769874478</v>
+        <v>0.5513549013449073</v>
       </c>
       <c r="AJ5">
-        <v>0.5541494008287603</v>
+        <v>0.4418970698125507</v>
       </c>
       <c r="AK5">
-        <v>0.6295521375254468</v>
+        <v>0.4693505353102098</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco BBVA Perú, S.A. (BVL:BBVAC1)</t>
+          <t>Scotiabank Perú S.A.A. (BVL:SCOTIAC1)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0843</v>
+        <v>-0.0203</v>
       </c>
       <c r="E6">
-        <v>0.09669999999999999</v>
+        <v>-0.0429</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>542.7</v>
+        <v>275.7</v>
       </c>
       <c r="L6">
-        <v>0.4060606060606061</v>
+        <v>0.33002154656452</v>
       </c>
       <c r="M6">
-        <v>272.8</v>
+        <v>325.6</v>
       </c>
       <c r="N6">
-        <v>0.08329008029798797</v>
+        <v>0.1225765162067537</v>
       </c>
       <c r="O6">
-        <v>0.5026718260549106</v>
+        <v>1.180993833877403</v>
       </c>
       <c r="P6">
-        <v>272.8</v>
+        <v>325.6</v>
       </c>
       <c r="Q6">
-        <v>0.08329008029798797</v>
+        <v>0.1225765162067537</v>
       </c>
       <c r="R6">
-        <v>0.5026718260549106</v>
+        <v>1.180993833877403</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4283.6</v>
+        <v>446.2</v>
       </c>
       <c r="V6">
-        <v>1.307849662626324</v>
+        <v>0.1679780145314912</v>
       </c>
       <c r="W6">
-        <v>0.236862779329609</v>
+        <v>0.1060099204060445</v>
       </c>
       <c r="X6">
-        <v>0.1158359007584044</v>
+        <v>0.09318507218626362</v>
       </c>
       <c r="Y6">
-        <v>0.1210268785712045</v>
+        <v>0.0128248482197809</v>
       </c>
       <c r="Z6">
-        <v>0.3604271729457135</v>
+        <v>0.1207033564028839</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08024286393926255</v>
+        <v>0.06795345285977052</v>
       </c>
       <c r="AC6">
-        <v>-0.08024286393926255</v>
+        <v>-0.06795345285977052</v>
       </c>
       <c r="AD6">
-        <v>4663</v>
+        <v>3735.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4663</v>
+        <v>3735.5</v>
       </c>
       <c r="AG6">
-        <v>379.3999999999996</v>
+        <v>3289.3</v>
       </c>
       <c r="AH6">
-        <v>0.5874053638688383</v>
+        <v>0.5844206639757189</v>
       </c>
       <c r="AI6">
-        <v>0.6321340454952146</v>
+        <v>0.5453443896172151</v>
       </c>
       <c r="AJ6">
-        <v>0.1038115303581688</v>
+        <v>0.5532326426264801</v>
       </c>
       <c r="AK6">
-        <v>0.1226640801810539</v>
+        <v>0.5136641888937473</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.08349999999999999</v>
+        <v>0.0609</v>
       </c>
       <c r="E7">
-        <v>0.0617</v>
+        <v>0.0168</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,85 +1222,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>382.5</v>
+        <v>313.4</v>
       </c>
       <c r="L7">
-        <v>0.3212665882748195</v>
+        <v>0.2712011076497058</v>
       </c>
       <c r="M7">
-        <v>188.912</v>
+        <v>156.6</v>
       </c>
       <c r="N7">
-        <v>0.06848359615733189</v>
+        <v>0.06217740014293655</v>
       </c>
       <c r="O7">
-        <v>0.4938875816993464</v>
+        <v>0.4996809189534142</v>
       </c>
       <c r="P7">
-        <v>188.9</v>
+        <v>135.2</v>
       </c>
       <c r="Q7">
-        <v>0.06847924596701106</v>
+        <v>0.05368061621535774</v>
       </c>
       <c r="R7">
-        <v>0.4938562091503268</v>
+        <v>0.431397574984046</v>
       </c>
       <c r="S7">
-        <v>0.01200000000000045</v>
+        <v>21.40000000000001</v>
       </c>
       <c r="T7">
-        <v>6.352163970526199e-05</v>
+        <v>0.136653895274585</v>
       </c>
       <c r="U7">
-        <v>956.9</v>
+        <v>1141.5</v>
       </c>
       <c r="V7">
-        <v>0.3468914264999093</v>
+        <v>0.4532279838005241</v>
       </c>
       <c r="W7">
-        <v>0.1619321789932687</v>
+        <v>0.131763716628127</v>
       </c>
       <c r="X7">
-        <v>0.1195900339795681</v>
+        <v>0.09861525397188617</v>
       </c>
       <c r="Y7">
-        <v>0.04234214501370064</v>
+        <v>0.0331484626562408</v>
       </c>
       <c r="Z7">
-        <v>0.6081937065794849</v>
+        <v>0.2016437208815369</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08125929503154064</v>
+        <v>0.06868784312101561</v>
       </c>
       <c r="AC7">
-        <v>-0.08125929503154064</v>
+        <v>-0.06868784312101561</v>
       </c>
       <c r="AD7">
-        <v>4309.3</v>
+        <v>4252.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4309.3</v>
+        <v>4252.2</v>
       </c>
       <c r="AG7">
-        <v>3352.4</v>
+        <v>3110.7</v>
       </c>
       <c r="AH7">
-        <v>0.6097088202835395</v>
+        <v>0.628020322561588</v>
       </c>
       <c r="AI7">
-        <v>0.6431119136806602</v>
+        <v>0.6255167036879036</v>
       </c>
       <c r="AJ7">
-        <v>0.5485934968662555</v>
+        <v>0.5525909082834456</v>
       </c>
       <c r="AK7">
-        <v>0.5836554197569553</v>
+        <v>0.5499434269146454</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0626</v>
+        <v>0.0442</v>
       </c>
       <c r="E2">
-        <v>0.0418</v>
+        <v>0.0033</v>
       </c>
       <c r="F2">
-        <v>0.112</v>
+        <v>0.198</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3690.8</v>
+        <v>3651.2</v>
       </c>
       <c r="L2">
-        <v>0.328541290201978</v>
+        <v>0.3122204834834065</v>
       </c>
       <c r="M2">
-        <v>1995</v>
+        <v>2404.55</v>
       </c>
       <c r="N2">
-        <v>0.06564270625629282</v>
+        <v>0.06429484368482412</v>
       </c>
       <c r="O2">
-        <v>0.5405332177305733</v>
+        <v>0.6585643076248905</v>
       </c>
       <c r="P2">
-        <v>1951</v>
+        <v>2372.9</v>
       </c>
       <c r="Q2">
-        <v>0.06419494732131693</v>
+        <v>0.06344855984684002</v>
       </c>
       <c r="R2">
-        <v>0.528611683103934</v>
+        <v>0.6498959246275197</v>
       </c>
       <c r="S2">
-        <v>44.00000000000003</v>
+        <v>31.64999999999998</v>
       </c>
       <c r="T2">
-        <v>0.02205513784461154</v>
+        <v>0.01316254600652928</v>
       </c>
       <c r="U2">
-        <v>14046.4</v>
+        <v>22108</v>
       </c>
       <c r="V2">
-        <v>0.4621772978237551</v>
+        <v>0.5911419617741747</v>
       </c>
       <c r="W2">
-        <v>0.1863576061320755</v>
+        <v>0.1453665987780041</v>
       </c>
       <c r="X2">
-        <v>0.08729077069043828</v>
+        <v>0.08930765648908363</v>
       </c>
       <c r="Y2">
-        <v>0.09906683544163719</v>
+        <v>0.05605894228892043</v>
       </c>
       <c r="Z2">
-        <v>0.3589243038071747</v>
+        <v>0.2968149180315386</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06776231979339066</v>
+        <v>0.07125836004454614</v>
       </c>
       <c r="AC2">
-        <v>-0.06776231979339066</v>
+        <v>-0.07125836004454614</v>
       </c>
       <c r="AD2">
-        <v>30689.2</v>
+        <v>26370.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>30689.2</v>
+        <v>26370.2</v>
       </c>
       <c r="AG2">
-        <v>16642.8</v>
+        <v>4262.200000000001</v>
       </c>
       <c r="AH2">
-        <v>0.502434472258149</v>
+        <v>0.4135269488309367</v>
       </c>
       <c r="AI2">
-        <v>0.5670395293578557</v>
+        <v>0.5116592224080592</v>
       </c>
       <c r="AJ2">
-        <v>0.3538416399841818</v>
+        <v>0.102306713713065</v>
       </c>
       <c r="AK2">
-        <v>0.4152871836588031</v>
+        <v>0.1448220559553662</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0626</v>
+        <v>0.0687</v>
       </c>
       <c r="E3">
-        <v>0.0418</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F3">
-        <v>0.112</v>
+        <v>0.156</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1326.3</v>
+        <v>1402.7</v>
       </c>
       <c r="L3">
-        <v>0.3060857123075857</v>
+        <v>0.3005120294791868</v>
       </c>
       <c r="M3">
-        <v>549.5</v>
+        <v>780.3</v>
       </c>
       <c r="N3">
-        <v>0.04608082383623906</v>
+        <v>0.05358504041368228</v>
       </c>
       <c r="O3">
-        <v>0.4143104878232677</v>
+        <v>0.556284308832965</v>
       </c>
       <c r="P3">
-        <v>526.9</v>
+        <v>749.9</v>
       </c>
       <c r="Q3">
-        <v>0.04418559796053569</v>
+        <v>0.05149740075127559</v>
       </c>
       <c r="R3">
-        <v>0.3972706024278067</v>
+        <v>0.5346118200613103</v>
       </c>
       <c r="S3">
-        <v>22.60000000000002</v>
+        <v>30.39999999999998</v>
       </c>
       <c r="T3">
-        <v>0.04112829845313926</v>
+        <v>0.03895937459951298</v>
       </c>
       <c r="U3">
-        <v>3501.9</v>
+        <v>4494.5</v>
       </c>
       <c r="V3">
-        <v>0.2936677652267982</v>
+        <v>0.3086479099568051</v>
       </c>
       <c r="W3">
-        <v>0.1946405247941768</v>
+        <v>0.1697629104287945</v>
       </c>
       <c r="X3">
-        <v>0.08267412208850056</v>
+        <v>0.08100165359762035</v>
       </c>
       <c r="Y3">
-        <v>0.1119664027056762</v>
+        <v>0.08876125683117411</v>
       </c>
       <c r="Z3">
-        <v>0.4888590543452508</v>
+        <v>0.3154384186517993</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06756868562128299</v>
+        <v>0.07125667153303947</v>
       </c>
       <c r="AC3">
-        <v>-0.06756868562128299</v>
+        <v>-0.07125667153303947</v>
       </c>
       <c r="AD3">
-        <v>10259.4</v>
+        <v>7911.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10259.4</v>
+        <v>7911.4</v>
       </c>
       <c r="AG3">
-        <v>6757.5</v>
+        <v>3416.9</v>
       </c>
       <c r="AH3">
-        <v>0.4624663610423682</v>
+        <v>0.3520355266026796</v>
       </c>
       <c r="AI3">
-        <v>0.5488922535324299</v>
+        <v>0.4633350707764027</v>
       </c>
       <c r="AJ3">
-        <v>0.3617079358962006</v>
+        <v>0.1900516163481434</v>
       </c>
       <c r="AK3">
-        <v>0.4448884733889869</v>
+        <v>0.2716050364058376</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08019999999999999</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="E4">
-        <v>0.0805</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1269.7</v>
+        <v>1332.4</v>
       </c>
       <c r="L4">
-        <v>0.3646048702044567</v>
+        <v>0.3541827268135783</v>
       </c>
       <c r="M4">
-        <v>711</v>
+        <v>1078.7</v>
       </c>
       <c r="N4">
-        <v>0.07268526564368885</v>
+        <v>0.078400732622031</v>
       </c>
       <c r="O4">
-        <v>0.559974797196188</v>
+        <v>0.8095917141999399</v>
       </c>
       <c r="P4">
-        <v>711</v>
+        <v>1078.7</v>
       </c>
       <c r="Q4">
-        <v>0.07268526564368885</v>
+        <v>0.078400732622031</v>
       </c>
       <c r="R4">
-        <v>0.559974797196188</v>
+        <v>0.8095917141999399</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>7874.4</v>
+        <v>11062</v>
       </c>
       <c r="V4">
-        <v>0.8049969842259683</v>
+        <v>0.8039945344070705</v>
       </c>
       <c r="W4">
-        <v>0.2340676560051618</v>
+        <v>0.2163127475810118</v>
       </c>
       <c r="X4">
-        <v>0.08299781168955206</v>
+        <v>0.08204490455354797</v>
       </c>
       <c r="Y4">
-        <v>0.1510698443156097</v>
+        <v>0.1342678430274638</v>
       </c>
       <c r="Z4">
-        <v>0.520530335869419</v>
+        <v>0.5538314317261686</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06758387462960216</v>
+        <v>0.07125693721420721</v>
       </c>
       <c r="AC4">
-        <v>-0.06758387462960216</v>
+        <v>-0.07125693721420721</v>
       </c>
       <c r="AD4">
-        <v>8580.299999999999</v>
+        <v>8275</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8580.299999999999</v>
+        <v>8275</v>
       </c>
       <c r="AG4">
-        <v>705.8999999999996</v>
+        <v>-2787</v>
       </c>
       <c r="AH4">
-        <v>0.4672806090773437</v>
+        <v>0.3755593678802567</v>
       </c>
       <c r="AI4">
-        <v>0.5805816439765069</v>
+        <v>0.5560744837411212</v>
       </c>
       <c r="AJ4">
-        <v>0.06730677549152346</v>
+        <v>-0.2540148380393372</v>
       </c>
       <c r="AK4">
-        <v>0.1022391518452001</v>
+        <v>-0.7297530831871383</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0716</v>
+        <v>0.0442</v>
       </c>
       <c r="E5">
-        <v>0.062</v>
+        <v>0.0033</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>505.7</v>
+        <v>456.8</v>
       </c>
       <c r="L5">
-        <v>0.3542805100182149</v>
+        <v>0.3251939915996298</v>
       </c>
       <c r="M5">
-        <v>252.3</v>
+        <v>251.1</v>
       </c>
       <c r="N5">
-        <v>0.07187419878642851</v>
+        <v>0.07145702902675014</v>
       </c>
       <c r="O5">
-        <v>0.4989123986553293</v>
+        <v>0.5496935201401051</v>
       </c>
       <c r="P5">
-        <v>252.3</v>
+        <v>251.1</v>
       </c>
       <c r="Q5">
-        <v>0.07187419878642851</v>
+        <v>0.07145702902675014</v>
       </c>
       <c r="R5">
-        <v>0.4989123986553293</v>
+        <v>0.5496935201401051</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1082.4</v>
+        <v>2222.4</v>
       </c>
       <c r="V5">
-        <v>0.3083497136996838</v>
+        <v>0.6324416619237336</v>
       </c>
       <c r="W5">
-        <v>0.1863576061320755</v>
+        <v>0.1453665987780041</v>
       </c>
       <c r="X5">
-        <v>0.08729077069043828</v>
+        <v>0.08930765648908363</v>
       </c>
       <c r="Y5">
-        <v>0.09906683544163719</v>
+        <v>0.05605894228892043</v>
       </c>
       <c r="Z5">
-        <v>0.4614936954413191</v>
+        <v>0.2372082812658313</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06776231979339066</v>
+        <v>0.07125836004454614</v>
       </c>
       <c r="AC5">
-        <v>-0.06776231979339066</v>
+        <v>-0.07125836004454614</v>
       </c>
       <c r="AD5">
-        <v>3861.8</v>
+        <v>3535.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3861.8</v>
+        <v>3535.7</v>
       </c>
       <c r="AG5">
-        <v>2779.4</v>
+        <v>1313.3</v>
       </c>
       <c r="AH5">
-        <v>0.5238398828013727</v>
+        <v>0.501539072584649</v>
       </c>
       <c r="AI5">
-        <v>0.5513549013449073</v>
+        <v>0.5071212403723412</v>
       </c>
       <c r="AJ5">
-        <v>0.4418970698125507</v>
+        <v>0.2720568433699998</v>
       </c>
       <c r="AK5">
-        <v>0.4693505353102098</v>
+        <v>0.2765016737899235</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0203</v>
+        <v>-0.0622</v>
       </c>
       <c r="E6">
-        <v>-0.0429</v>
+        <v>-0.153</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>275.7</v>
+        <v>164.2</v>
       </c>
       <c r="L6">
-        <v>0.33002154656452</v>
+        <v>0.21826399042935</v>
       </c>
       <c r="M6">
-        <v>325.6</v>
+        <v>178.3</v>
       </c>
       <c r="N6">
-        <v>0.1225765162067537</v>
+        <v>0.0793608403436151</v>
       </c>
       <c r="O6">
-        <v>1.180993833877403</v>
+        <v>1.085870889159562</v>
       </c>
       <c r="P6">
-        <v>325.6</v>
+        <v>178.3</v>
       </c>
       <c r="Q6">
-        <v>0.1225765162067537</v>
+        <v>0.0793608403436151</v>
       </c>
       <c r="R6">
-        <v>1.180993833877403</v>
+        <v>1.085870889159562</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>446.2</v>
+        <v>477.7</v>
       </c>
       <c r="V6">
-        <v>0.1679780145314912</v>
+        <v>0.2126229581163484</v>
       </c>
       <c r="W6">
-        <v>0.1060099204060445</v>
+        <v>0.05303446271115274</v>
       </c>
       <c r="X6">
-        <v>0.09318507218626362</v>
+        <v>0.09319268809776148</v>
       </c>
       <c r="Y6">
-        <v>0.0128248482197809</v>
+        <v>-0.04015822538660874</v>
       </c>
       <c r="Z6">
-        <v>0.1207033564028839</v>
+        <v>0.1204470132406859</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06795345285977052</v>
+        <v>0.07125890841992216</v>
       </c>
       <c r="AC6">
-        <v>-0.06795345285977052</v>
+        <v>-0.07125890841992216</v>
       </c>
       <c r="AD6">
-        <v>3735.5</v>
+        <v>2747</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3735.5</v>
+        <v>2747</v>
       </c>
       <c r="AG6">
-        <v>3289.3</v>
+        <v>2269.3</v>
       </c>
       <c r="AH6">
-        <v>0.5844206639757189</v>
+        <v>0.5500931173278331</v>
       </c>
       <c r="AI6">
-        <v>0.5453443896172151</v>
+        <v>0.4670497823721436</v>
       </c>
       <c r="AJ6">
-        <v>0.5532326426264801</v>
+        <v>0.5025022143489815</v>
       </c>
       <c r="AK6">
-        <v>0.5136641888937473</v>
+        <v>0.4199374525805438</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,10 +1204,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0609</v>
+        <v>0.0236</v>
       </c>
       <c r="E7">
-        <v>0.0168</v>
+        <v>-0.0347</v>
+      </c>
+      <c r="F7">
+        <v>0.24</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,85 +1225,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>313.4</v>
+        <v>295.1</v>
       </c>
       <c r="L7">
-        <v>0.2712011076497058</v>
+        <v>0.2664078721675544</v>
       </c>
       <c r="M7">
-        <v>156.6</v>
+        <v>116.15</v>
       </c>
       <c r="N7">
-        <v>0.06217740014293655</v>
+        <v>0.03501235907638512</v>
       </c>
       <c r="O7">
-        <v>0.4996809189534142</v>
+        <v>0.3935953913927482</v>
       </c>
       <c r="P7">
-        <v>135.2</v>
+        <v>114.9</v>
       </c>
       <c r="Q7">
-        <v>0.05368061621535774</v>
+        <v>0.03463555796708265</v>
       </c>
       <c r="R7">
-        <v>0.431397574984046</v>
+        <v>0.3893595391392748</v>
       </c>
       <c r="S7">
-        <v>21.40000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>0.136653895274585</v>
+        <v>0.01076194575979337</v>
       </c>
       <c r="U7">
-        <v>1141.5</v>
+        <v>3851.4</v>
       </c>
       <c r="V7">
-        <v>0.4532279838005241</v>
+        <v>1.160969433894013</v>
       </c>
       <c r="W7">
-        <v>0.131763716628127</v>
+        <v>0.1165988383578964</v>
       </c>
       <c r="X7">
-        <v>0.09861525397188617</v>
+        <v>0.0923541380307258</v>
       </c>
       <c r="Y7">
-        <v>0.0331484626562408</v>
+        <v>0.0242447003271706</v>
       </c>
       <c r="Z7">
-        <v>0.2016437208815369</v>
+        <v>0.1963450085082246</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06868784312101561</v>
+        <v>0.07183030490352399</v>
       </c>
       <c r="AC7">
-        <v>-0.06868784312101561</v>
+        <v>-0.07183030490352399</v>
       </c>
       <c r="AD7">
-        <v>4252.2</v>
+        <v>3901.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4252.2</v>
+        <v>3901.1</v>
       </c>
       <c r="AG7">
-        <v>3110.7</v>
+        <v>49.69999999999982</v>
       </c>
       <c r="AH7">
-        <v>0.628020322561588</v>
+        <v>0.5404308374315994</v>
       </c>
       <c r="AI7">
-        <v>0.6255167036879036</v>
+        <v>0.5797530056918665</v>
       </c>
       <c r="AJ7">
-        <v>0.5525909082834456</v>
+        <v>0.014760476374328</v>
       </c>
       <c r="AK7">
-        <v>0.5499434269146454</v>
+        <v>0.01727193744569933</v>
       </c>
       <c r="AL7">
         <v>0</v>

--- a/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.1453665987780041</v>
       </c>
       <c r="X2">
-        <v>0.08930765648908363</v>
+        <v>0.08929588499792825</v>
       </c>
       <c r="Y2">
-        <v>0.05605894228892043</v>
+        <v>0.05607071378007582</v>
       </c>
       <c r="Z2">
         <v>0.2968149180315386</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07125836004454614</v>
+        <v>0.07125249241614776</v>
       </c>
       <c r="AC2">
-        <v>-0.07125836004454614</v>
+        <v>-0.07125249241614776</v>
       </c>
       <c r="AD2">
         <v>26370.2</v>
@@ -773,10 +773,10 @@
         <v>0.1697629104287945</v>
       </c>
       <c r="X3">
-        <v>0.08100165359762035</v>
+        <v>0.08099212938998845</v>
       </c>
       <c r="Y3">
-        <v>0.08876125683117411</v>
+        <v>0.08877078103880601</v>
       </c>
       <c r="Z3">
         <v>0.3154384186517993</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07125667153303947</v>
+        <v>0.07125050018485674</v>
       </c>
       <c r="AC3">
-        <v>-0.07125667153303947</v>
+        <v>-0.07125050018485674</v>
       </c>
       <c r="AD3">
         <v>7911.4</v>
@@ -895,10 +895,10 @@
         <v>0.2163127475810118</v>
       </c>
       <c r="X4">
-        <v>0.08204490455354797</v>
+        <v>0.08203509808250793</v>
       </c>
       <c r="Y4">
-        <v>0.1342678430274638</v>
+        <v>0.1342776494985038</v>
       </c>
       <c r="Z4">
         <v>0.5538314317261686</v>
@@ -907,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07125693721420721</v>
+        <v>0.0712508136552321</v>
       </c>
       <c r="AC4">
-        <v>-0.07125693721420721</v>
+        <v>-0.0712508136552321</v>
       </c>
       <c r="AD4">
         <v>8275</v>
@@ -1017,10 +1017,10 @@
         <v>0.1453665987780041</v>
       </c>
       <c r="X5">
-        <v>0.08930765648908363</v>
+        <v>0.08929588499792825</v>
       </c>
       <c r="Y5">
-        <v>0.05605894228892043</v>
+        <v>0.05607071378007582</v>
       </c>
       <c r="Z5">
         <v>0.2372082812658313</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07125836004454614</v>
+        <v>0.07125249241614776</v>
       </c>
       <c r="AC5">
-        <v>-0.07125836004454614</v>
+        <v>-0.07125249241614776</v>
       </c>
       <c r="AD5">
         <v>3535.7</v>
@@ -1139,10 +1139,10 @@
         <v>0.05303446271115274</v>
       </c>
       <c r="X6">
-        <v>0.09319268809776148</v>
+        <v>0.09317986546713064</v>
       </c>
       <c r="Y6">
-        <v>-0.04015822538660874</v>
+        <v>-0.0401454027559779</v>
       </c>
       <c r="Z6">
         <v>0.1204470132406859</v>
@@ -1151,10 +1151,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07125890841992216</v>
+        <v>0.07125313943014738</v>
       </c>
       <c r="AC6">
-        <v>-0.07125890841992216</v>
+        <v>-0.07125313943014738</v>
       </c>
       <c r="AD6">
         <v>2747</v>
@@ -1264,10 +1264,10 @@
         <v>0.1165988383578964</v>
       </c>
       <c r="X7">
-        <v>0.0923541380307258</v>
+        <v>0.0923415422793501</v>
       </c>
       <c r="Y7">
-        <v>0.0242447003271706</v>
+        <v>0.02425729607854631</v>
       </c>
       <c r="Z7">
         <v>0.1963450085082246</v>
@@ -1276,10 +1276,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07183030490352399</v>
+        <v>0.07182451628461234</v>
       </c>
       <c r="AC7">
-        <v>-0.07183030490352399</v>
+        <v>-0.07182451628461234</v>
       </c>
       <c r="AD7">
         <v>3901.1</v>
